--- a/tools/sched-template.xlsx
+++ b/tools/sched-template.xlsx
@@ -1800,7 +1800,7 @@
       <c r="K32" s="45" t="n"/>
       <c r="L32" s="45" t="n"/>
       <c r="M32" s="43" t="n"/>
-      <c r="N32" s="55" t="n"/>
+      <c r="N32" s="30" t="n"/>
       <c r="O32" s="45" t="n"/>
       <c r="P32" s="43" t="n"/>
       <c r="Q32" s="30" t="n"/>
@@ -1823,7 +1823,7 @@
       <c r="K33" s="45" t="n"/>
       <c r="L33" s="45" t="n"/>
       <c r="M33" s="43" t="n"/>
-      <c r="N33" s="55" t="n"/>
+      <c r="N33" s="30" t="n"/>
       <c r="O33" s="45" t="n"/>
       <c r="P33" s="43" t="n"/>
       <c r="Q33" s="30" t="n"/>
